--- a/lang/de/headTags.xlsx
+++ b/lang/de/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1205</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1209</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1862">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1869">
   <si>
     <t>en</t>
   </si>
@@ -4480,6 +4480,18 @@
     <t>Shulker</t>
   </si>
   <si>
+    <t>Sift (Inspired)</t>
+  </si>
+  <si>
+    <t>Sift (Inspiriert)</t>
+  </si>
+  <si>
+    <t>Sift (Vanilla)</t>
+  </si>
+  <si>
+    <t>Sift (Vanille)</t>
+  </si>
+  <si>
     <t>Silent Hill</t>
   </si>
   <si>
@@ -5188,6 +5200,9 @@
     <t>ULTRAKILL</t>
   </si>
   <si>
+    <t>Umamusume</t>
+  </si>
+  <si>
     <t>Umineko - When They Cry</t>
   </si>
   <si>
@@ -5438,6 +5453,12 @@
   </si>
   <si>
     <t>Winter</t>
+  </si>
+  <si>
+    <t>Winter Drop</t>
+  </si>
+  <si>
+    <t>Winterkollektion</t>
   </si>
   <si>
     <t>Witcher</t>
@@ -5949,7 +5970,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1205"/>
+  <dimension ref="A1:B1209"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -13657,20 +13678,20 @@
         <v>1487</v>
       </c>
       <c r="B963" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="964" spans="1:2">
       <c r="A964" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="B964" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="965" spans="1:2">
       <c r="A965" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="B965" t="s">
         <v>1491</v>
@@ -13713,28 +13734,28 @@
         <v>1500</v>
       </c>
       <c r="B970" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="971" spans="1:2">
       <c r="A971" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="B971" t="s">
-        <v>1501</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="972" spans="1:2">
       <c r="A972" t="s">
-        <v>1502</v>
+        <v>1504</v>
       </c>
       <c r="B972" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="973" spans="1:2">
       <c r="A973" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="B973" t="s">
         <v>1505</v>
@@ -13777,36 +13798,36 @@
         <v>1514</v>
       </c>
       <c r="B978" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="979" spans="1:2">
       <c r="A979" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="B979" t="s">
-        <v>1515</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="980" spans="1:2">
       <c r="A980" t="s">
-        <v>1516</v>
+        <v>1518</v>
       </c>
       <c r="B980" t="s">
-        <v>1516</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="981" spans="1:2">
       <c r="A981" t="s">
-        <v>1517</v>
+        <v>1519</v>
       </c>
       <c r="B981" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="982" spans="1:2">
       <c r="A982" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="B982" t="s">
         <v>1520</v>
@@ -13849,44 +13870,44 @@
         <v>1529</v>
       </c>
       <c r="B987" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="988" spans="1:2">
       <c r="A988" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="B988" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="989" spans="1:2">
       <c r="A989" t="s">
-        <v>1531</v>
+        <v>1533</v>
       </c>
       <c r="B989" t="s">
-        <v>1531</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="990" spans="1:2">
       <c r="A990" t="s">
-        <v>1532</v>
+        <v>1534</v>
       </c>
       <c r="B990" t="s">
-        <v>1532</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="991" spans="1:2">
       <c r="A991" t="s">
-        <v>1533</v>
+        <v>1535</v>
       </c>
       <c r="B991" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="992" spans="1:2">
       <c r="A992" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="B992" t="s">
         <v>1536</v>
@@ -13897,28 +13918,28 @@
         <v>1537</v>
       </c>
       <c r="B993" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="994" spans="1:2">
       <c r="A994" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="B994" t="s">
-        <v>1538</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="995" spans="1:2">
       <c r="A995" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="B995" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="996" spans="1:2">
       <c r="A996" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="B996" t="s">
         <v>1542</v>
@@ -13945,140 +13966,140 @@
         <v>1547</v>
       </c>
       <c r="B999" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="1000" spans="1:2">
       <c r="A1000" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="B1000" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="1001" spans="1:2">
       <c r="A1001" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="B1001" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="1002" spans="1:2">
       <c r="A1002" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="B1002" t="s">
-        <v>1551</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="1003" spans="1:2">
       <c r="A1003" t="s">
-        <v>1552</v>
+        <v>1554</v>
       </c>
       <c r="B1003" t="s">
-        <v>1552</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="1004" spans="1:2">
       <c r="A1004" t="s">
-        <v>1553</v>
+        <v>1555</v>
       </c>
       <c r="B1004" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="1005" spans="1:2">
       <c r="A1005" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="B1005" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="1006" spans="1:2">
       <c r="A1006" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="B1006" t="s">
-        <v>1556</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="1007" spans="1:2">
       <c r="A1007" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
       <c r="B1007" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="1008" spans="1:2">
       <c r="A1008" t="s">
-        <v>1558</v>
+        <v>1560</v>
       </c>
       <c r="B1008" t="s">
-        <v>1558</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="1009" spans="1:2">
       <c r="A1009" t="s">
-        <v>1559</v>
+        <v>1561</v>
       </c>
       <c r="B1009" t="s">
-        <v>1559</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="1010" spans="1:2">
       <c r="A1010" t="s">
-        <v>1560</v>
+        <v>1562</v>
       </c>
       <c r="B1010" t="s">
-        <v>1560</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="1011" spans="1:2">
       <c r="A1011" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="B1011" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="1012" spans="1:2">
       <c r="A1012" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="B1012" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="1013" spans="1:2">
       <c r="A1013" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="B1013" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="1014" spans="1:2">
       <c r="A1014" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="B1014" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="1015" spans="1:2">
       <c r="A1015" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="B1015" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="1016" spans="1:2">
       <c r="A1016" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="B1016" t="s">
         <v>1569</v>
@@ -14089,36 +14110,36 @@
         <v>1570</v>
       </c>
       <c r="B1017" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="1018" spans="1:2">
       <c r="A1018" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="B1018" t="s">
-        <v>1571</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
-        <v>1572</v>
+        <v>1574</v>
       </c>
       <c r="B1019" t="s">
-        <v>1572</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="1020" spans="1:2">
       <c r="A1020" t="s">
-        <v>1573</v>
+        <v>1575</v>
       </c>
       <c r="B1020" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="1021" spans="1:2">
       <c r="A1021" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="B1021" t="s">
         <v>1576</v>
@@ -14129,44 +14150,44 @@
         <v>1577</v>
       </c>
       <c r="B1022" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="1023" spans="1:2">
       <c r="A1023" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="B1023" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="1024" spans="1:2">
       <c r="A1024" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="B1024" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="1025" spans="1:2">
       <c r="A1025" t="s">
-        <v>1580</v>
+        <v>1582</v>
       </c>
       <c r="B1025" t="s">
-        <v>1580</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="1026" spans="1:2">
       <c r="A1026" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="B1026" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="1027" spans="1:2">
       <c r="A1027" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="B1027" t="s">
         <v>1584</v>
@@ -14177,44 +14198,44 @@
         <v>1585</v>
       </c>
       <c r="B1028" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="1029" spans="1:2">
       <c r="A1029" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="B1029" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="1030" spans="1:2">
       <c r="A1030" t="s">
-        <v>1587</v>
+        <v>1589</v>
       </c>
       <c r="B1030" t="s">
-        <v>1587</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="1031" spans="1:2">
       <c r="A1031" t="s">
-        <v>1588</v>
+        <v>1590</v>
       </c>
       <c r="B1031" t="s">
-        <v>1588</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="1032" spans="1:2">
       <c r="A1032" t="s">
-        <v>1589</v>
+        <v>1591</v>
       </c>
       <c r="B1032" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="1033" spans="1:2">
       <c r="A1033" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="B1033" t="s">
         <v>1592</v>
@@ -14225,20 +14246,20 @@
         <v>1593</v>
       </c>
       <c r="B1034" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="1035" spans="1:2">
       <c r="A1035" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="B1035" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="1036" spans="1:2">
       <c r="A1036" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="B1036" t="s">
         <v>1597</v>
@@ -14257,36 +14278,36 @@
         <v>1600</v>
       </c>
       <c r="B1038" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="1039" spans="1:2">
       <c r="A1039" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="B1039" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="1040" spans="1:2">
       <c r="A1040" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="B1040" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="1041" spans="1:2">
       <c r="A1041" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="B1041" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="1042" spans="1:2">
       <c r="A1042" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="B1042" t="s">
         <v>1607</v>
@@ -14297,60 +14318,60 @@
         <v>1608</v>
       </c>
       <c r="B1043" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="1044" spans="1:2">
       <c r="A1044" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="B1044" t="s">
-        <v>1609</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="1045" spans="1:2">
       <c r="A1045" t="s">
-        <v>1610</v>
+        <v>1612</v>
       </c>
       <c r="B1045" t="s">
-        <v>1610</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="1046" spans="1:2">
       <c r="A1046" t="s">
-        <v>1611</v>
+        <v>1613</v>
       </c>
       <c r="B1046" t="s">
-        <v>1611</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="1047" spans="1:2">
       <c r="A1047" t="s">
-        <v>1612</v>
+        <v>1614</v>
       </c>
       <c r="B1047" t="s">
-        <v>1612</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="1048" spans="1:2">
       <c r="A1048" t="s">
-        <v>1613</v>
+        <v>1615</v>
       </c>
       <c r="B1048" t="s">
-        <v>1613</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="1049" spans="1:2">
       <c r="A1049" t="s">
-        <v>1614</v>
+        <v>1616</v>
       </c>
       <c r="B1049" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="1050" spans="1:2">
       <c r="A1050" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="B1050" t="s">
         <v>1617</v>
@@ -14361,60 +14382,60 @@
         <v>1618</v>
       </c>
       <c r="B1051" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="1052" spans="1:2">
       <c r="A1052" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="B1052" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="1053" spans="1:2">
       <c r="A1053" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="B1053" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="1054" spans="1:2">
       <c r="A1054" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="B1054" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="1055" spans="1:2">
       <c r="A1055" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="B1055" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="1056" spans="1:2">
       <c r="A1056" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="B1056" t="s">
-        <v>1625</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="1057" spans="1:2">
       <c r="A1057" t="s">
-        <v>1626</v>
+        <v>1628</v>
       </c>
       <c r="B1057" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="1058" spans="1:2">
       <c r="A1058" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="B1058" t="s">
         <v>1629</v>
@@ -14441,44 +14462,44 @@
         <v>1634</v>
       </c>
       <c r="B1061" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="1062" spans="1:2">
       <c r="A1062" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="B1062" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="1063" spans="1:2">
       <c r="A1063" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="B1063" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="1064" spans="1:2">
       <c r="A1064" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
       <c r="B1064" t="s">
-        <v>1638</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="1065" spans="1:2">
       <c r="A1065" t="s">
-        <v>1639</v>
+        <v>1641</v>
       </c>
       <c r="B1065" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="1066" spans="1:2">
       <c r="A1066" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="B1066" t="s">
         <v>1642</v>
@@ -14489,20 +14510,20 @@
         <v>1643</v>
       </c>
       <c r="B1067" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="1068" spans="1:2">
       <c r="A1068" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
       <c r="B1068" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="1069" spans="1:2">
       <c r="A1069" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="B1069" t="s">
         <v>1647</v>
@@ -14537,52 +14558,52 @@
         <v>1654</v>
       </c>
       <c r="B1073" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="1074" spans="1:2">
       <c r="A1074" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="B1074" t="s">
-        <v>1655</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="1075" spans="1:2">
       <c r="A1075" t="s">
-        <v>1656</v>
+        <v>1658</v>
       </c>
       <c r="B1075" t="s">
-        <v>1656</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="1076" spans="1:2">
       <c r="A1076" t="s">
-        <v>1657</v>
+        <v>1659</v>
       </c>
       <c r="B1076" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="1077" spans="1:2">
       <c r="A1077" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="B1077" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="1078" spans="1:2">
       <c r="A1078" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="B1078" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="1079" spans="1:2">
       <c r="A1079" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="B1079" t="s">
         <v>1663</v>
@@ -14625,20 +14646,20 @@
         <v>1672</v>
       </c>
       <c r="B1084" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="1085" spans="1:2">
       <c r="A1085" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="B1085" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="1086" spans="1:2">
       <c r="A1086" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="B1086" t="s">
         <v>1676</v>
@@ -14649,84 +14670,84 @@
         <v>1677</v>
       </c>
       <c r="B1087" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="1088" spans="1:2">
       <c r="A1088" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="B1088" t="s">
-        <v>1678</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="1089" spans="1:2">
       <c r="A1089" t="s">
-        <v>1679</v>
+        <v>1681</v>
       </c>
       <c r="B1089" t="s">
-        <v>1679</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="1090" spans="1:2">
       <c r="A1090" t="s">
-        <v>1680</v>
+        <v>1682</v>
       </c>
       <c r="B1090" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="1091" spans="1:2">
       <c r="A1091" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="B1091" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="1092" spans="1:2">
       <c r="A1092" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="B1092" t="s">
-        <v>1683</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="1093" spans="1:2">
       <c r="A1093" t="s">
-        <v>1684</v>
+        <v>1686</v>
       </c>
       <c r="B1093" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="1094" spans="1:2">
       <c r="A1094" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="B1094" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="1095" spans="1:2">
       <c r="A1095" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="B1095" t="s">
-        <v>1687</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="1096" spans="1:2">
       <c r="A1096" t="s">
-        <v>1688</v>
+        <v>1690</v>
       </c>
       <c r="B1096" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="1097" spans="1:2">
       <c r="A1097" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="B1097" t="s">
         <v>1691</v>
@@ -14737,44 +14758,44 @@
         <v>1692</v>
       </c>
       <c r="B1098" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="1099" spans="1:2">
       <c r="A1099" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="B1099" t="s">
-        <v>1693</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="1100" spans="1:2">
       <c r="A1100" t="s">
-        <v>1694</v>
+        <v>1696</v>
       </c>
       <c r="B1100" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="1101" spans="1:2">
       <c r="A1101" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="B1101" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="1102" spans="1:2">
       <c r="A1102" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="B1102" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="1103" spans="1:2">
       <c r="A1103" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="B1103" t="s">
         <v>1700</v>
@@ -14801,28 +14822,28 @@
         <v>1705</v>
       </c>
       <c r="B1106" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="1107" spans="1:2">
       <c r="A1107" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="B1107" t="s">
-        <v>1706</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="1108" spans="1:2">
       <c r="A1108" t="s">
-        <v>1707</v>
+        <v>1709</v>
       </c>
       <c r="B1108" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="1109" spans="1:2">
       <c r="A1109" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="B1109" t="s">
         <v>1710</v>
@@ -14849,92 +14870,92 @@
         <v>1715</v>
       </c>
       <c r="B1112" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="1113" spans="1:2">
       <c r="A1113" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="B1113" t="s">
-        <v>1716</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="1114" spans="1:2">
       <c r="A1114" t="s">
-        <v>1717</v>
+        <v>1719</v>
       </c>
       <c r="B1114" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="1115" spans="1:2">
       <c r="A1115" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="B1115" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="1116" spans="1:2">
       <c r="A1116" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="B1116" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="1117" spans="1:2">
       <c r="A1117" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="B1117" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="1118" spans="1:2">
       <c r="A1118" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="B1118" t="s">
-        <v>1723</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="1119" spans="1:2">
       <c r="A1119" t="s">
-        <v>1724</v>
+        <v>1726</v>
       </c>
       <c r="B1119" t="s">
-        <v>1724</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="1120" spans="1:2">
       <c r="A1120" t="s">
-        <v>1725</v>
+        <v>1727</v>
       </c>
       <c r="B1120" t="s">
-        <v>1725</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="1121" spans="1:2">
       <c r="A1121" t="s">
-        <v>1726</v>
+        <v>1728</v>
       </c>
       <c r="B1121" t="s">
-        <v>1726</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="1122" spans="1:2">
       <c r="A1122" t="s">
-        <v>1727</v>
+        <v>1729</v>
       </c>
       <c r="B1122" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="1123" spans="1:2">
       <c r="A1123" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="B1123" t="s">
         <v>1730</v>
@@ -14945,28 +14966,28 @@
         <v>1731</v>
       </c>
       <c r="B1124" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="1125" spans="1:2">
       <c r="A1125" t="s">
+        <v>1732</v>
+      </c>
+      <c r="B1125" t="s">
         <v>1733</v>
-      </c>
-      <c r="B1125" t="s">
-        <v>1734</v>
       </c>
     </row>
     <row r="1126" spans="1:2">
       <c r="A1126" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B1126" t="s">
         <v>1735</v>
-      </c>
-      <c r="B1126" t="s">
-        <v>1736</v>
       </c>
     </row>
     <row r="1127" spans="1:2">
       <c r="A1127" t="s">
-        <v>1737</v>
+        <v>1736</v>
       </c>
       <c r="B1127" t="s">
         <v>1737</v>
@@ -14993,36 +15014,36 @@
         <v>1742</v>
       </c>
       <c r="B1130" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="1131" spans="1:2">
       <c r="A1131" t="s">
+        <v>1743</v>
+      </c>
+      <c r="B1131" t="s">
         <v>1744</v>
-      </c>
-      <c r="B1131" t="s">
-        <v>1745</v>
       </c>
     </row>
     <row r="1132" spans="1:2">
       <c r="A1132" t="s">
+        <v>1745</v>
+      </c>
+      <c r="B1132" t="s">
         <v>1746</v>
-      </c>
-      <c r="B1132" t="s">
-        <v>1747</v>
       </c>
     </row>
     <row r="1133" spans="1:2">
       <c r="A1133" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B1133" t="s">
         <v>1748</v>
-      </c>
-      <c r="B1133" t="s">
-        <v>1749</v>
       </c>
     </row>
     <row r="1134" spans="1:2">
       <c r="A1134" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
       <c r="B1134" t="s">
         <v>1750</v>
@@ -15049,84 +15070,84 @@
         <v>1755</v>
       </c>
       <c r="B1137" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="1138" spans="1:2">
       <c r="A1138" t="s">
+        <v>1756</v>
+      </c>
+      <c r="B1138" t="s">
         <v>1757</v>
-      </c>
-      <c r="B1138" t="s">
-        <v>1758</v>
       </c>
     </row>
     <row r="1139" spans="1:2">
       <c r="A1139" t="s">
+        <v>1758</v>
+      </c>
+      <c r="B1139" t="s">
         <v>1759</v>
-      </c>
-      <c r="B1139" t="s">
-        <v>1760</v>
       </c>
     </row>
     <row r="1140" spans="1:2">
       <c r="A1140" t="s">
+        <v>1760</v>
+      </c>
+      <c r="B1140" t="s">
         <v>1761</v>
-      </c>
-      <c r="B1140" t="s">
-        <v>1762</v>
       </c>
     </row>
     <row r="1141" spans="1:2">
       <c r="A1141" t="s">
+        <v>1762</v>
+      </c>
+      <c r="B1141" t="s">
         <v>1763</v>
-      </c>
-      <c r="B1141" t="s">
-        <v>1764</v>
       </c>
     </row>
     <row r="1142" spans="1:2">
       <c r="A1142" t="s">
+        <v>1764</v>
+      </c>
+      <c r="B1142" t="s">
         <v>1765</v>
-      </c>
-      <c r="B1142" t="s">
-        <v>1766</v>
       </c>
     </row>
     <row r="1143" spans="1:2">
       <c r="A1143" t="s">
+        <v>1766</v>
+      </c>
+      <c r="B1143" t="s">
         <v>1767</v>
-      </c>
-      <c r="B1143" t="s">
-        <v>1768</v>
       </c>
     </row>
     <row r="1144" spans="1:2">
       <c r="A1144" t="s">
+        <v>1768</v>
+      </c>
+      <c r="B1144" t="s">
         <v>1769</v>
-      </c>
-      <c r="B1144" t="s">
-        <v>1770</v>
       </c>
     </row>
     <row r="1145" spans="1:2">
       <c r="A1145" t="s">
+        <v>1770</v>
+      </c>
+      <c r="B1145" t="s">
         <v>1771</v>
-      </c>
-      <c r="B1145" t="s">
-        <v>1772</v>
       </c>
     </row>
     <row r="1146" spans="1:2">
       <c r="A1146" t="s">
+        <v>1772</v>
+      </c>
+      <c r="B1146" t="s">
         <v>1773</v>
-      </c>
-      <c r="B1146" t="s">
-        <v>1774</v>
       </c>
     </row>
     <row r="1147" spans="1:2">
       <c r="A1147" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="B1147" t="s">
         <v>1775</v>
@@ -15137,28 +15158,28 @@
         <v>1776</v>
       </c>
       <c r="B1148" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="1149" spans="1:2">
       <c r="A1149" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="B1149" t="s">
-        <v>1777</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="1150" spans="1:2">
       <c r="A1150" t="s">
-        <v>1778</v>
+        <v>1780</v>
       </c>
       <c r="B1150" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="1151" spans="1:2">
       <c r="A1151" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="B1151" t="s">
         <v>1781</v>
@@ -15169,20 +15190,20 @@
         <v>1782</v>
       </c>
       <c r="B1152" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="1153" spans="1:2">
       <c r="A1153" t="s">
+        <v>1783</v>
+      </c>
+      <c r="B1153" t="s">
         <v>1784</v>
-      </c>
-      <c r="B1153" t="s">
-        <v>1785</v>
       </c>
     </row>
     <row r="1154" spans="1:2">
       <c r="A1154" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="B1154" t="s">
         <v>1786</v>
@@ -15193,44 +15214,44 @@
         <v>1787</v>
       </c>
       <c r="B1155" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="1156" spans="1:2">
       <c r="A1156" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="B1156" t="s">
-        <v>1788</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="1157" spans="1:2">
       <c r="A1157" t="s">
-        <v>1789</v>
+        <v>1791</v>
       </c>
       <c r="B1157" t="s">
-        <v>1789</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="1158" spans="1:2">
       <c r="A1158" t="s">
-        <v>1790</v>
+        <v>1792</v>
       </c>
       <c r="B1158" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="1159" spans="1:2">
       <c r="A1159" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="B1159" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="1160" spans="1:2">
       <c r="A1160" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="B1160" t="s">
         <v>1794</v>
@@ -15249,28 +15270,28 @@
         <v>1797</v>
       </c>
       <c r="B1162" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="1163" spans="1:2">
       <c r="A1163" t="s">
+        <v>1798</v>
+      </c>
+      <c r="B1163" t="s">
         <v>1799</v>
-      </c>
-      <c r="B1163" t="s">
-        <v>1800</v>
       </c>
     </row>
     <row r="1164" spans="1:2">
       <c r="A1164" t="s">
+        <v>1800</v>
+      </c>
+      <c r="B1164" t="s">
         <v>1801</v>
-      </c>
-      <c r="B1164" t="s">
-        <v>1802</v>
       </c>
     </row>
     <row r="1165" spans="1:2">
       <c r="A1165" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="B1165" t="s">
         <v>1803</v>
@@ -15289,12 +15310,12 @@
         <v>1806</v>
       </c>
       <c r="B1167" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="1168" spans="1:2">
       <c r="A1168" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="B1168" t="s">
         <v>1808</v>
@@ -15305,12 +15326,12 @@
         <v>1809</v>
       </c>
       <c r="B1169" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="1170" spans="1:2">
       <c r="A1170" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="B1170" t="s">
         <v>1811</v>
@@ -15337,12 +15358,12 @@
         <v>1816</v>
       </c>
       <c r="B1173" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="1174" spans="1:2">
       <c r="A1174" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
       <c r="B1174" t="s">
         <v>1818</v>
@@ -15353,68 +15374,68 @@
         <v>1819</v>
       </c>
       <c r="B1175" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="B1176" t="s">
-        <v>1820</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
-        <v>1821</v>
+        <v>1823</v>
       </c>
       <c r="B1177" t="s">
-        <v>1821</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>1822</v>
+        <v>1825</v>
       </c>
       <c r="B1178" t="s">
-        <v>1822</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>1823</v>
+        <v>1826</v>
       </c>
       <c r="B1179" t="s">
-        <v>1823</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
       <c r="A1180" t="s">
-        <v>1824</v>
+        <v>1827</v>
       </c>
       <c r="B1180" t="s">
-        <v>1824</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="1181" spans="1:2">
       <c r="A1181" t="s">
-        <v>1825</v>
+        <v>1828</v>
       </c>
       <c r="B1181" t="s">
-        <v>1826</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" t="s">
-        <v>1827</v>
+        <v>1829</v>
       </c>
       <c r="B1182" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
     </row>
     <row r="1183" spans="1:2">
       <c r="A1183" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
       <c r="B1183" t="s">
         <v>1830</v>
@@ -15425,12 +15446,12 @@
         <v>1831</v>
       </c>
       <c r="B1184" t="s">
-        <v>1832</v>
+        <v>1831</v>
       </c>
     </row>
     <row r="1185" spans="1:2">
       <c r="A1185" t="s">
-        <v>1833</v>
+        <v>1832</v>
       </c>
       <c r="B1185" t="s">
         <v>1833</v>
@@ -15441,163 +15462,195 @@
         <v>1834</v>
       </c>
       <c r="B1186" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="1187" spans="1:2">
       <c r="A1187" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="B1187" t="s">
-        <v>1835</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="1188" spans="1:2">
       <c r="A1188" t="s">
-        <v>1836</v>
+        <v>1838</v>
       </c>
       <c r="B1188" t="s">
-        <v>1837</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="1189" spans="1:2">
       <c r="A1189" t="s">
-        <v>1838</v>
+        <v>1840</v>
       </c>
       <c r="B1189" t="s">
-        <v>1838</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="1190" spans="1:2">
       <c r="A1190" t="s">
-        <v>1839</v>
+        <v>1841</v>
       </c>
       <c r="B1190" t="s">
-        <v>1839</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="1191" spans="1:2">
       <c r="A1191" t="s">
-        <v>1840</v>
+        <v>1842</v>
       </c>
       <c r="B1191" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="1192" spans="1:2">
       <c r="A1192" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
       <c r="B1192" t="s">
-        <v>1842</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="1193" spans="1:2">
       <c r="A1193" t="s">
-        <v>1843</v>
+        <v>1845</v>
       </c>
       <c r="B1193" t="s">
-        <v>1843</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="1194" spans="1:2">
       <c r="A1194" t="s">
-        <v>1844</v>
+        <v>1846</v>
       </c>
       <c r="B1194" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="1195" spans="1:2">
       <c r="A1195" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
       <c r="B1195" t="s">
-        <v>1846</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="1196" spans="1:2">
       <c r="A1196" t="s">
-        <v>1847</v>
+        <v>1849</v>
       </c>
       <c r="B1196" t="s">
-        <v>1847</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="1197" spans="1:2">
       <c r="A1197" t="s">
-        <v>1848</v>
+        <v>1850</v>
       </c>
       <c r="B1197" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="1198" spans="1:2">
       <c r="A1198" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
       <c r="B1198" t="s">
-        <v>1850</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="1199" spans="1:2">
       <c r="A1199" t="s">
-        <v>1851</v>
+        <v>1853</v>
       </c>
       <c r="B1199" t="s">
-        <v>1851</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="1200" spans="1:2">
       <c r="A1200" t="s">
-        <v>1852</v>
+        <v>1854</v>
       </c>
       <c r="B1200" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="1201" spans="1:2">
       <c r="A1201" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="B1201" t="s">
-        <v>1854</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="1202" spans="1:2">
       <c r="A1202" t="s">
-        <v>1855</v>
+        <v>1857</v>
       </c>
       <c r="B1202" t="s">
-        <v>1855</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="1203" spans="1:2">
       <c r="A1203" t="s">
-        <v>1856</v>
+        <v>1858</v>
       </c>
       <c r="B1203" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="1204" spans="1:2">
       <c r="A1204" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="B1204" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="1205" spans="1:2">
       <c r="A1205" t="s">
-        <v>1860</v>
+        <v>1861</v>
       </c>
       <c r="B1205" t="s">
         <v>1861</v>
       </c>
     </row>
+    <row r="1206" spans="1:2">
+      <c r="A1206" t="s">
+        <v>1862</v>
+      </c>
+      <c r="B1206" t="s">
+        <v>1862</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:2">
+      <c r="A1207" t="s">
+        <v>1863</v>
+      </c>
+      <c r="B1207" t="s">
+        <v>1864</v>
+      </c>
+    </row>
+    <row r="1208" spans="1:2">
+      <c r="A1208" t="s">
+        <v>1865</v>
+      </c>
+      <c r="B1208" t="s">
+        <v>1866</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:2">
+      <c r="A1209" t="s">
+        <v>1867</v>
+      </c>
+      <c r="B1209" t="s">
+        <v>1868</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1205"/>
+  <autoFilter ref="A1:B1209"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
